--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0002T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.16039347851347</v>
+        <v>2.301063940258438</v>
       </c>
       <c r="D2" t="n">
-        <v>13.38904849948816</v>
+        <v>2.175720381166826</v>
       </c>
       <c r="E2" t="n">
-        <v>2.465952841320136</v>
+        <v>0.400717336714522</v>
       </c>
       <c r="F2" t="n">
-        <v>2.537051626106568</v>
+        <v>0.4122708892423173</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>9.228487795873194</v>
+        <v>1.499629266829394</v>
       </c>
       <c r="D3" t="n">
-        <v>8.314945247275025</v>
+        <v>1.351178602682192</v>
       </c>
       <c r="E3" t="n">
-        <v>2.465952841320136</v>
+        <v>0.400717336714522</v>
       </c>
       <c r="F3" t="n">
-        <v>2.537051626106568</v>
+        <v>0.4122708892423173</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
